--- a/assets/files/Risk_Assessment_Template.xlsx
+++ b/assets/files/Risk_Assessment_Template.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/403e8c2cb7d71729/Documents/[06] Internal Audit Files/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Colby.Kellersberger\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="362" documentId="8_{0A60F589-CB05-481D-80F1-8244999A83D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D0385603-DFF0-402F-A761-97D9D540C090}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5044CE0-489E-4777-83B3-70FDE7429852}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{C2087629-0EDA-46AC-AED4-A2841B02CC28}"/>
+    <workbookView xWindow="15156" yWindow="2064" windowWidth="29064" windowHeight="21948" xr2:uid="{C2087629-0EDA-46AC-AED4-A2841B02CC28}"/>
   </bookViews>
   <sheets>
     <sheet name="Template" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" concurrentCalc="0" concurrentManualCount="20"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -960,36 +960,6 @@
     <xf numFmtId="0" fontId="2" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1078,13 +1048,43 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="40% - Accent3" xfId="1" builtinId="39"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="40">
+  <dxfs count="8">
     <dxf>
       <font>
         <b/>
@@ -1100,10 +1100,11 @@
       <font>
         <b/>
         <i val="0"/>
+        <color theme="2"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFF3300"/>
+          <bgColor rgb="FFCC0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1174,360 +1175,6 @@
         </patternFill>
       </fill>
     </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="2"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFCC0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF8ED973"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF66"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF66"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF8ED973"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="2"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFCC0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF8ED973"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF3300"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF66"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF66"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF8ED973"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF3300"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF8ED973"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF3300"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF66"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF66"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF8ED973"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF3300"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF8ED973"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF3300"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF66"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF66"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF8ED973"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF3300"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -1549,10 +1196,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1873,50 +1516,50 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80FDE253-9743-4A1A-BB9D-2C6D91E51B62}">
   <dimension ref="B1:X31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.140625" customWidth="1"/>
-    <col min="2" max="2" width="11.140625" customWidth="1"/>
-    <col min="3" max="3" width="25.5703125" customWidth="1"/>
-    <col min="4" max="4" width="29.85546875" customWidth="1"/>
-    <col min="5" max="5" width="18.28515625" customWidth="1"/>
-    <col min="6" max="6" width="10.5703125" customWidth="1"/>
-    <col min="7" max="7" width="10.85546875" customWidth="1"/>
-    <col min="8" max="8" width="12.85546875" customWidth="1"/>
-    <col min="9" max="9" width="25.42578125" customWidth="1"/>
-    <col min="10" max="10" width="23.28515625" customWidth="1"/>
-    <col min="11" max="11" width="10.85546875" customWidth="1"/>
+    <col min="1" max="1" width="2.109375" customWidth="1"/>
+    <col min="2" max="2" width="11.109375" customWidth="1"/>
+    <col min="3" max="3" width="25.5546875" customWidth="1"/>
+    <col min="4" max="4" width="29.88671875" customWidth="1"/>
+    <col min="5" max="5" width="18.33203125" customWidth="1"/>
+    <col min="6" max="6" width="10.5546875" customWidth="1"/>
+    <col min="7" max="7" width="10.88671875" customWidth="1"/>
+    <col min="8" max="8" width="12.88671875" customWidth="1"/>
+    <col min="9" max="9" width="25.44140625" customWidth="1"/>
+    <col min="10" max="10" width="23.33203125" customWidth="1"/>
+    <col min="11" max="11" width="10.88671875" customWidth="1"/>
     <col min="12" max="12" width="10" customWidth="1"/>
-    <col min="13" max="13" width="12.28515625" customWidth="1"/>
-    <col min="14" max="14" width="4.28515625" customWidth="1"/>
-    <col min="16" max="16" width="10.7109375" customWidth="1"/>
-    <col min="17" max="17" width="12.42578125" customWidth="1"/>
-    <col min="18" max="18" width="12.140625" customWidth="1"/>
-    <col min="19" max="19" width="11.140625" customWidth="1"/>
-    <col min="20" max="20" width="10.85546875" customWidth="1"/>
-    <col min="21" max="21" width="11.85546875" customWidth="1"/>
-    <col min="22" max="22" width="3.85546875" customWidth="1"/>
-    <col min="23" max="23" width="11.5703125" customWidth="1"/>
-    <col min="24" max="24" width="10.28515625" customWidth="1"/>
+    <col min="13" max="13" width="12.33203125" customWidth="1"/>
+    <col min="14" max="14" width="4.33203125" customWidth="1"/>
+    <col min="16" max="16" width="10.6640625" customWidth="1"/>
+    <col min="17" max="17" width="12.44140625" customWidth="1"/>
+    <col min="18" max="18" width="12.109375" customWidth="1"/>
+    <col min="19" max="19" width="11.109375" customWidth="1"/>
+    <col min="20" max="20" width="10.88671875" customWidth="1"/>
+    <col min="21" max="21" width="11.88671875" customWidth="1"/>
+    <col min="22" max="22" width="3.88671875" customWidth="1"/>
+    <col min="23" max="23" width="11.5546875" customWidth="1"/>
+    <col min="24" max="24" width="10.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:24" ht="27" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B1" s="36" t="s">
+    <row r="1" spans="2:24" ht="26.4" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B1" s="73" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
-      <c r="I1" s="36"/>
-      <c r="J1" s="36"/>
-      <c r="K1" s="36"/>
-      <c r="L1" s="36"/>
-      <c r="M1" s="36"/>
-    </row>
-    <row r="2" spans="2:24" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C1" s="73"/>
+      <c r="D1" s="73"/>
+      <c r="E1" s="73"/>
+      <c r="F1" s="73"/>
+      <c r="G1" s="73"/>
+      <c r="H1" s="73"/>
+      <c r="I1" s="73"/>
+      <c r="J1" s="73"/>
+      <c r="K1" s="73"/>
+      <c r="L1" s="73"/>
+      <c r="M1" s="73"/>
+    </row>
+    <row r="2" spans="2:24" ht="35.1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B2" s="1"/>
       <c r="C2" s="2" t="s">
         <v>1</v>
@@ -1927,9 +1570,9 @@
       <c r="E2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
-      <c r="H2" s="37"/>
+      <c r="F2" s="74"/>
+      <c r="G2" s="74"/>
+      <c r="H2" s="74"/>
       <c r="I2" s="2" t="s">
         <v>3</v>
       </c>
@@ -1939,7 +1582,7 @@
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
-      <c r="O2" s="46" t="s">
+      <c r="O2" s="36" t="s">
         <v>24</v>
       </c>
       <c r="W2" s="3" t="s">
@@ -1949,7 +1592,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="2:24" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:24" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
@@ -1962,7 +1605,7 @@
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
-      <c r="O3" s="47" t="s">
+      <c r="O3" s="37" t="s">
         <v>29</v>
       </c>
       <c r="W3" s="32" t="s">
@@ -1972,23 +1615,23 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="2:24" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:24" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
-      <c r="F4" s="38" t="s">
+      <c r="F4" s="75" t="s">
         <v>14</v>
       </c>
-      <c r="G4" s="39"/>
-      <c r="H4" s="39"/>
+      <c r="G4" s="76"/>
+      <c r="H4" s="76"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
-      <c r="K4" s="38" t="s">
+      <c r="K4" s="75" t="s">
         <v>15</v>
       </c>
-      <c r="L4" s="39"/>
-      <c r="M4" s="39"/>
+      <c r="L4" s="76"/>
+      <c r="M4" s="76"/>
       <c r="W4" s="32" t="s">
         <v>20</v>
       </c>
@@ -1996,7 +1639,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="2:24" ht="35.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:24" ht="35.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B5" s="20" t="s">
         <v>5</v>
       </c>
@@ -2033,10 +1676,10 @@
       <c r="M5" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="O5" s="43" t="s">
+      <c r="O5" s="68" t="s">
         <v>31</v>
       </c>
-      <c r="P5" s="44"/>
+      <c r="P5" s="69"/>
       <c r="Q5" s="5" t="str">
         <f>X$7</f>
         <v>Very Low</v>
@@ -2064,13 +1707,13 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="2:24" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="69"/>
-      <c r="C6" s="70"/>
-      <c r="D6" s="75" t="s">
+    <row r="6" spans="2:24" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="59"/>
+      <c r="C6" s="60"/>
+      <c r="D6" s="65" t="s">
         <v>34</v>
       </c>
-      <c r="E6" s="70"/>
+      <c r="E6" s="60"/>
       <c r="F6" s="19" t="s">
         <v>20</v>
       </c>
@@ -2081,8 +1724,8 @@
         <f t="array" ref="H6">IFERROR(_xlfn.XLOOKUP(F6, P$6:P$10, _xlfn.XLOOKUP(G6, Q$5:U$5, Q$6:U$10)),"")</f>
         <v>Critical</v>
       </c>
-      <c r="I6" s="66"/>
-      <c r="J6" s="66"/>
+      <c r="I6" s="56"/>
+      <c r="J6" s="56"/>
       <c r="K6" s="19" t="s">
         <v>21</v>
       </c>
@@ -2093,7 +1736,7 @@
         <f t="array" ref="M6">IFERROR(_xlfn.XLOOKUP(K6, P$6:P$10, _xlfn.XLOOKUP(L6, Q$5:U$5, Q$6:U$10)),"")</f>
         <v>Sustainable</v>
       </c>
-      <c r="O6" s="40" t="s">
+      <c r="O6" s="70" t="s">
         <v>30</v>
       </c>
       <c r="P6" s="27" t="str">
@@ -2109,10 +1752,10 @@
       <c r="S6" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="T6" s="48" t="s">
+      <c r="T6" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="U6" s="49" t="s">
+      <c r="U6" s="39" t="s">
         <v>27</v>
       </c>
       <c r="W6" s="32" t="s">
@@ -2122,13 +1765,13 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="2:24" ht="50.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="71"/>
-      <c r="C7" s="72"/>
-      <c r="D7" s="75" t="s">
+    <row r="7" spans="2:24" ht="50.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B7" s="61"/>
+      <c r="C7" s="62"/>
+      <c r="D7" s="65" t="s">
         <v>34</v>
       </c>
-      <c r="E7" s="72"/>
+      <c r="E7" s="62"/>
       <c r="F7" s="17" t="s">
         <v>21</v>
       </c>
@@ -2139,8 +1782,8 @@
         <f t="array" ref="H7">IFERROR(_xlfn.XLOOKUP(F7, P$6:P$10, _xlfn.XLOOKUP(G7, Q$5:U$5, Q$6:U$10)),"")</f>
         <v>Moderate</v>
       </c>
-      <c r="I7" s="67"/>
-      <c r="J7" s="67"/>
+      <c r="I7" s="57"/>
+      <c r="J7" s="57"/>
       <c r="K7" s="17" t="s">
         <v>20</v>
       </c>
@@ -2151,7 +1794,7 @@
         <f t="array" ref="M7">IFERROR(_xlfn.XLOOKUP(K7, P$6:P$10, _xlfn.XLOOKUP(L7, Q$5:U$5, Q$6:U$10)),"")</f>
         <v>Moderate</v>
       </c>
-      <c r="O7" s="41"/>
+      <c r="O7" s="71"/>
       <c r="P7" s="28" t="str">
         <f>W$4</f>
         <v>High</v>
@@ -2165,10 +1808,10 @@
       <c r="S7" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="T7" s="50" t="s">
+      <c r="T7" s="40" t="s">
         <v>27</v>
       </c>
-      <c r="U7" s="51" t="s">
+      <c r="U7" s="41" t="s">
         <v>27</v>
       </c>
       <c r="W7" s="34" t="s">
@@ -2178,28 +1821,28 @@
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="2:24" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="71"/>
-      <c r="C8" s="72"/>
-      <c r="D8" s="75" t="s">
+    <row r="8" spans="2:24" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="61"/>
+      <c r="C8" s="62"/>
+      <c r="D8" s="65" t="s">
         <v>34</v>
       </c>
-      <c r="E8" s="72"/>
+      <c r="E8" s="62"/>
       <c r="F8" s="17"/>
       <c r="G8" s="17"/>
       <c r="H8" s="19" t="str" cm="1">
         <f t="array" ref="H8">IFERROR(_xlfn.XLOOKUP(F8, P$6:P$10, _xlfn.XLOOKUP(G8, Q$5:U$5, Q$6:U$10)),"")</f>
         <v/>
       </c>
-      <c r="I8" s="67"/>
-      <c r="J8" s="67"/>
+      <c r="I8" s="57"/>
+      <c r="J8" s="57"/>
       <c r="K8" s="17"/>
       <c r="L8" s="17"/>
       <c r="M8" s="25" t="str" cm="1">
         <f t="array" ref="M8">IFERROR(_xlfn.XLOOKUP(K8, P$6:P$10, _xlfn.XLOOKUP(L8, Q$5:U$5, Q$6:U$10)),"")</f>
         <v/>
       </c>
-      <c r="O8" s="41"/>
+      <c r="O8" s="71"/>
       <c r="P8" s="28" t="str">
         <f>W$5</f>
         <v>Medium</v>
@@ -2216,32 +1859,32 @@
       <c r="T8" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="U8" s="51" t="s">
+      <c r="U8" s="41" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="2:24" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="71"/>
-      <c r="C9" s="72"/>
-      <c r="D9" s="75" t="s">
+    <row r="9" spans="2:24" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="61"/>
+      <c r="C9" s="62"/>
+      <c r="D9" s="65" t="s">
         <v>34</v>
       </c>
-      <c r="E9" s="72"/>
+      <c r="E9" s="62"/>
       <c r="F9" s="17"/>
       <c r="G9" s="17"/>
       <c r="H9" s="19" t="str" cm="1">
         <f t="array" ref="H9">IFERROR(_xlfn.XLOOKUP(F9, P$6:P$10, _xlfn.XLOOKUP(G9, Q$5:U$5, Q$6:U$10)),"")</f>
         <v/>
       </c>
-      <c r="I9" s="67"/>
-      <c r="J9" s="67"/>
+      <c r="I9" s="57"/>
+      <c r="J9" s="57"/>
       <c r="K9" s="17"/>
       <c r="L9" s="17"/>
       <c r="M9" s="25" t="str" cm="1">
         <f t="array" ref="M9">IFERROR(_xlfn.XLOOKUP(K9, P$6:P$10, _xlfn.XLOOKUP(L9, Q$5:U$5, Q$6:U$10)),"")</f>
         <v/>
       </c>
-      <c r="O9" s="41"/>
+      <c r="O9" s="71"/>
       <c r="P9" s="28" t="str">
         <f>W$6</f>
         <v>Low</v>
@@ -2258,32 +1901,32 @@
       <c r="T9" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="U9" s="51" t="s">
+      <c r="U9" s="41" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="2:24" ht="50.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="71"/>
-      <c r="C10" s="72"/>
-      <c r="D10" s="75" t="s">
+    <row r="10" spans="2:24" ht="50.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B10" s="61"/>
+      <c r="C10" s="62"/>
+      <c r="D10" s="65" t="s">
         <v>34</v>
       </c>
-      <c r="E10" s="72"/>
+      <c r="E10" s="62"/>
       <c r="F10" s="17"/>
       <c r="G10" s="17"/>
       <c r="H10" s="19" t="str" cm="1">
         <f t="array" ref="H10">IFERROR(_xlfn.XLOOKUP(F10, P$6:P$10, _xlfn.XLOOKUP(G10, Q$5:U$5, Q$6:U$10)),"")</f>
         <v/>
       </c>
-      <c r="I10" s="67"/>
-      <c r="J10" s="67"/>
+      <c r="I10" s="57"/>
+      <c r="J10" s="57"/>
       <c r="K10" s="17"/>
       <c r="L10" s="17"/>
       <c r="M10" s="25" t="str" cm="1">
         <f t="array" ref="M10">IFERROR(_xlfn.XLOOKUP(K10, P$6:P$10, _xlfn.XLOOKUP(L10, Q$5:U$5, Q$6:U$10)),"")</f>
         <v/>
       </c>
-      <c r="O10" s="42"/>
+      <c r="O10" s="72"/>
       <c r="P10" s="29" t="str">
         <f>W$7</f>
         <v>Very Low</v>
@@ -2304,59 +1947,59 @@
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="2:24" ht="50.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="71"/>
-      <c r="C11" s="72"/>
-      <c r="D11" s="75" t="s">
+    <row r="11" spans="2:24" ht="50.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B11" s="61"/>
+      <c r="C11" s="62"/>
+      <c r="D11" s="65" t="s">
         <v>34</v>
       </c>
-      <c r="E11" s="72"/>
+      <c r="E11" s="62"/>
       <c r="F11" s="17"/>
       <c r="G11" s="17"/>
       <c r="H11" s="19" t="str" cm="1">
         <f t="array" ref="H11">IFERROR(_xlfn.XLOOKUP(F11, P$6:P$10, _xlfn.XLOOKUP(G11, Q$5:U$5, Q$6:U$10)),"")</f>
         <v/>
       </c>
-      <c r="I11" s="67"/>
-      <c r="J11" s="67"/>
+      <c r="I11" s="57"/>
+      <c r="J11" s="57"/>
       <c r="K11" s="17"/>
       <c r="L11" s="17"/>
       <c r="M11" s="25" t="str" cm="1">
         <f t="array" ref="M11">IFERROR(_xlfn.XLOOKUP(K11, P$6:P$10, _xlfn.XLOOKUP(L11, Q$5:U$5, Q$6:U$10)),"")</f>
         <v/>
       </c>
-      <c r="O11" s="45" t="s">
+      <c r="O11" s="67" t="s">
         <v>32</v>
       </c>
-      <c r="P11" s="45"/>
-      <c r="Q11" s="45"/>
-      <c r="R11" s="45"/>
-    </row>
-    <row r="12" spans="2:24" ht="50.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="71"/>
-      <c r="C12" s="72"/>
-      <c r="D12" s="75" t="s">
+      <c r="P11" s="67"/>
+      <c r="Q11" s="67"/>
+      <c r="R11" s="67"/>
+    </row>
+    <row r="12" spans="2:24" ht="50.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B12" s="61"/>
+      <c r="C12" s="62"/>
+      <c r="D12" s="65" t="s">
         <v>34</v>
       </c>
-      <c r="E12" s="72"/>
+      <c r="E12" s="62"/>
       <c r="F12" s="17"/>
       <c r="G12" s="17"/>
       <c r="H12" s="19" t="str" cm="1">
         <f t="array" ref="H12">IFERROR(_xlfn.XLOOKUP(F12, P$6:P$10, _xlfn.XLOOKUP(G12, Q$5:U$5, Q$6:U$10)),"")</f>
         <v/>
       </c>
-      <c r="I12" s="67"/>
-      <c r="J12" s="67"/>
+      <c r="I12" s="57"/>
+      <c r="J12" s="57"/>
       <c r="K12" s="17"/>
       <c r="L12" s="17"/>
       <c r="M12" s="25" t="str" cm="1">
         <f t="array" ref="M12">IFERROR(_xlfn.XLOOKUP(K12, P$6:P$10, _xlfn.XLOOKUP(L12, Q$5:U$5, Q$6:U$10)),"")</f>
         <v/>
       </c>
-      <c r="O12" s="43" t="s">
+      <c r="O12" s="68" t="s">
         <v>31</v>
       </c>
-      <c r="P12" s="44"/>
+      <c r="P12" s="69"/>
       <c r="Q12" s="5" t="str">
         <f>X$7</f>
         <v>Very Low</v>
@@ -2378,296 +2021,296 @@
         <v>Very High</v>
       </c>
     </row>
-    <row r="13" spans="2:24" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="71"/>
-      <c r="C13" s="72"/>
-      <c r="D13" s="75" t="s">
+    <row r="13" spans="2:24" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="61"/>
+      <c r="C13" s="62"/>
+      <c r="D13" s="65" t="s">
         <v>34</v>
       </c>
-      <c r="E13" s="72"/>
+      <c r="E13" s="62"/>
       <c r="F13" s="17"/>
       <c r="G13" s="17"/>
       <c r="H13" s="19" t="str" cm="1">
         <f t="array" ref="H13">IFERROR(_xlfn.XLOOKUP(F13, P$6:P$10, _xlfn.XLOOKUP(G13, Q$5:U$5, Q$6:U$10)),"")</f>
         <v/>
       </c>
-      <c r="I13" s="67"/>
-      <c r="J13" s="67"/>
+      <c r="I13" s="57"/>
+      <c r="J13" s="57"/>
       <c r="K13" s="17"/>
       <c r="L13" s="17"/>
       <c r="M13" s="25" t="str" cm="1">
         <f t="array" ref="M13">IFERROR(_xlfn.XLOOKUP(K13, P$6:P$10, _xlfn.XLOOKUP(L13, Q$5:U$5, Q$6:U$10)),"")</f>
         <v/>
       </c>
-      <c r="O13" s="40" t="s">
+      <c r="O13" s="70" t="s">
         <v>30</v>
       </c>
       <c r="P13" s="27" t="str">
         <f>W$3</f>
         <v>Very High</v>
       </c>
-      <c r="Q13" s="52" t="str">
+      <c r="Q13" s="42" t="str">
         <f>IF(COUNTIFS($F$6:$F$31, $W3, $G$6:$G$31, $X$7)=0, "",COUNTIFS($F$6:$F$31, $W3, $G$6:$G$31, $X$7))</f>
         <v/>
       </c>
-      <c r="R13" s="53" t="str">
+      <c r="R13" s="43" t="str">
         <f>IF(COUNTIFS($F$6:$F$31, $W3, $G$6:$G$31, $X$6)=0, "",COUNTIFS($F$6:$F$31, $W3, $G$6:$G$31, $X$6))</f>
         <v/>
       </c>
-      <c r="S13" s="53" t="str">
+      <c r="S13" s="43" t="str">
         <f>IF(COUNTIFS($F$6:$F$31, $W3, $G$6:$G$31, $X$5)=0, "",COUNTIFS($F$6:$F$31, $W3, $G$6:$G$31, $X$5))</f>
         <v/>
       </c>
-      <c r="T13" s="54" t="str">
+      <c r="T13" s="44" t="str">
         <f>IF(COUNTIFS($F$6:$F$31, $W3, $G$6:$G$31, $X$4)=0, "",COUNTIFS($F$6:$F$31, $W3, $G$6:$G$31, $X$4))</f>
         <v/>
       </c>
-      <c r="U13" s="55" t="str">
+      <c r="U13" s="45" t="str">
         <f>IF(COUNTIFS($F$6:$F$31, $W3, $G$6:$G$31, $X$3)=0, "",COUNTIFS($F$6:$F$31, $W3, $G$6:$G$31, $X$3))</f>
         <v/>
       </c>
     </row>
-    <row r="14" spans="2:24" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="71"/>
-      <c r="C14" s="72"/>
-      <c r="D14" s="75" t="s">
+    <row r="14" spans="2:24" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="61"/>
+      <c r="C14" s="62"/>
+      <c r="D14" s="65" t="s">
         <v>34</v>
       </c>
-      <c r="E14" s="72"/>
+      <c r="E14" s="62"/>
       <c r="F14" s="17"/>
       <c r="G14" s="17"/>
       <c r="H14" s="19" t="str" cm="1">
         <f t="array" ref="H14">IFERROR(_xlfn.XLOOKUP(F14, P$6:P$10, _xlfn.XLOOKUP(G14, Q$5:U$5, Q$6:U$10)),"")</f>
         <v/>
       </c>
-      <c r="I14" s="67"/>
-      <c r="J14" s="67"/>
+      <c r="I14" s="57"/>
+      <c r="J14" s="57"/>
       <c r="K14" s="17"/>
       <c r="L14" s="17"/>
       <c r="M14" s="25" t="str" cm="1">
         <f t="array" ref="M14">IFERROR(_xlfn.XLOOKUP(K14, P$6:P$10, _xlfn.XLOOKUP(L14, Q$5:U$5, Q$6:U$10)),"")</f>
         <v/>
       </c>
-      <c r="O14" s="41"/>
+      <c r="O14" s="71"/>
       <c r="P14" s="28" t="str">
         <f>W$4</f>
         <v>High</v>
       </c>
-      <c r="Q14" s="56" t="str">
+      <c r="Q14" s="46" t="str">
         <f t="shared" ref="Q14:Q17" si="0">IF(COUNTIFS($F$6:$F$31, $W4, $G$6:$G$31, $X$7)=0, "",COUNTIFS($F$6:$F$31, $W4, $G$6:$G$31, $X$7))</f>
         <v/>
       </c>
-      <c r="R14" s="57" t="str">
+      <c r="R14" s="47" t="str">
         <f t="shared" ref="R14:R17" si="1">IF(COUNTIFS($F$6:$F$31, $W4, $G$6:$G$31, $X$6)=0, "",COUNTIFS($F$6:$F$31, $W4, $G$6:$G$31, $X$6))</f>
         <v/>
       </c>
-      <c r="S14" s="58" t="str">
+      <c r="S14" s="48" t="str">
         <f t="shared" ref="S14:S17" si="2">IF(COUNTIFS($F$6:$F$31, $W4, $G$6:$G$31, $X$5)=0, "",COUNTIFS($F$6:$F$31, $W4, $G$6:$G$31, $X$5))</f>
         <v/>
       </c>
-      <c r="T14" s="59">
+      <c r="T14" s="49">
         <f t="shared" ref="T14:T17" si="3">IF(COUNTIFS($F$6:$F$31, $W4, $G$6:$G$31, $X$4)=0, "",COUNTIFS($F$6:$F$31, $W4, $G$6:$G$31, $X$4))</f>
         <v>1</v>
       </c>
-      <c r="U14" s="60" t="str">
+      <c r="U14" s="50" t="str">
         <f t="shared" ref="U14:U17" si="4">IF(COUNTIFS($F$6:$F$31, $W4, $G$6:$G$31, $X$3)=0, "",COUNTIFS($F$6:$F$31, $W4, $G$6:$G$31, $X$3))</f>
         <v/>
       </c>
     </row>
-    <row r="15" spans="2:24" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="71"/>
-      <c r="C15" s="72"/>
-      <c r="D15" s="75" t="s">
+    <row r="15" spans="2:24" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="61"/>
+      <c r="C15" s="62"/>
+      <c r="D15" s="65" t="s">
         <v>34</v>
       </c>
-      <c r="E15" s="72"/>
+      <c r="E15" s="62"/>
       <c r="F15" s="17"/>
       <c r="G15" s="17"/>
       <c r="H15" s="19" t="str" cm="1">
         <f t="array" ref="H15">IFERROR(_xlfn.XLOOKUP(F15, P$6:P$10, _xlfn.XLOOKUP(G15, Q$5:U$5, Q$6:U$10)),"")</f>
         <v/>
       </c>
-      <c r="I15" s="67"/>
-      <c r="J15" s="67"/>
+      <c r="I15" s="57"/>
+      <c r="J15" s="57"/>
       <c r="K15" s="17"/>
       <c r="L15" s="17"/>
       <c r="M15" s="25" t="str" cm="1">
         <f t="array" ref="M15">IFERROR(_xlfn.XLOOKUP(K15, P$6:P$10, _xlfn.XLOOKUP(L15, Q$5:U$5, Q$6:U$10)),"")</f>
         <v/>
       </c>
-      <c r="O15" s="41"/>
+      <c r="O15" s="71"/>
       <c r="P15" s="28" t="str">
         <f>W$5</f>
         <v>Medium</v>
       </c>
-      <c r="Q15" s="56" t="str">
+      <c r="Q15" s="46" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="R15" s="57">
+      <c r="R15" s="47">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="S15" s="57" t="str">
+      <c r="S15" s="47" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="T15" s="58" t="str">
+      <c r="T15" s="48" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="U15" s="60" t="str">
+      <c r="U15" s="50" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="16" spans="2:24" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="71"/>
-      <c r="C16" s="72"/>
-      <c r="D16" s="75" t="s">
+    <row r="16" spans="2:24" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="61"/>
+      <c r="C16" s="62"/>
+      <c r="D16" s="65" t="s">
         <v>34</v>
       </c>
-      <c r="E16" s="72"/>
+      <c r="E16" s="62"/>
       <c r="F16" s="17"/>
       <c r="G16" s="17"/>
       <c r="H16" s="19" t="str" cm="1">
         <f t="array" ref="H16">IFERROR(_xlfn.XLOOKUP(F16, P$6:P$10, _xlfn.XLOOKUP(G16, Q$5:U$5, Q$6:U$10)),"")</f>
         <v/>
       </c>
-      <c r="I16" s="67"/>
-      <c r="J16" s="67"/>
+      <c r="I16" s="57"/>
+      <c r="J16" s="57"/>
       <c r="K16" s="17"/>
       <c r="L16" s="17"/>
       <c r="M16" s="25" t="str" cm="1">
         <f t="array" ref="M16">IFERROR(_xlfn.XLOOKUP(K16, P$6:P$10, _xlfn.XLOOKUP(L16, Q$5:U$5, Q$6:U$10)),"")</f>
         <v/>
       </c>
-      <c r="O16" s="41"/>
+      <c r="O16" s="71"/>
       <c r="P16" s="28" t="str">
         <f>W$6</f>
         <v>Low</v>
       </c>
-      <c r="Q16" s="56" t="str">
+      <c r="Q16" s="46" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="R16" s="61" t="str">
+      <c r="R16" s="51" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="S16" s="57" t="str">
+      <c r="S16" s="47" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="T16" s="58" t="str">
+      <c r="T16" s="48" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="U16" s="60" t="str">
+      <c r="U16" s="50" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="17" spans="2:21" ht="50.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="71"/>
-      <c r="C17" s="72"/>
-      <c r="D17" s="75" t="s">
+    <row r="17" spans="2:21" ht="50.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B17" s="61"/>
+      <c r="C17" s="62"/>
+      <c r="D17" s="65" t="s">
         <v>34</v>
       </c>
-      <c r="E17" s="72"/>
+      <c r="E17" s="62"/>
       <c r="F17" s="17"/>
       <c r="G17" s="17"/>
       <c r="H17" s="19" t="str" cm="1">
         <f t="array" ref="H17">IFERROR(_xlfn.XLOOKUP(F17, P$6:P$10, _xlfn.XLOOKUP(G17, Q$5:U$5, Q$6:U$10)),"")</f>
         <v/>
       </c>
-      <c r="I17" s="67"/>
-      <c r="J17" s="67"/>
+      <c r="I17" s="57"/>
+      <c r="J17" s="57"/>
       <c r="K17" s="17"/>
       <c r="L17" s="17"/>
       <c r="M17" s="25" t="str" cm="1">
         <f t="array" ref="M17">IFERROR(_xlfn.XLOOKUP(K17, P$6:P$10, _xlfn.XLOOKUP(L17, Q$5:U$5, Q$6:U$10)),"")</f>
         <v/>
       </c>
-      <c r="O17" s="42"/>
+      <c r="O17" s="72"/>
       <c r="P17" s="29" t="str">
         <f>W$7</f>
         <v>Very Low</v>
       </c>
-      <c r="Q17" s="62" t="str">
+      <c r="Q17" s="52" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="R17" s="63" t="str">
+      <c r="R17" s="53" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="S17" s="63" t="str">
+      <c r="S17" s="53" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="T17" s="64" t="str">
+      <c r="T17" s="54" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="U17" s="65" t="str">
+      <c r="U17" s="55" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="18" spans="2:21" ht="50.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="71"/>
-      <c r="C18" s="72"/>
-      <c r="D18" s="75" t="s">
+    <row r="18" spans="2:21" ht="50.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B18" s="61"/>
+      <c r="C18" s="62"/>
+      <c r="D18" s="65" t="s">
         <v>34</v>
       </c>
-      <c r="E18" s="72"/>
+      <c r="E18" s="62"/>
       <c r="F18" s="17"/>
       <c r="G18" s="17"/>
       <c r="H18" s="19" t="str" cm="1">
         <f t="array" ref="H18">IFERROR(_xlfn.XLOOKUP(F18, P$6:P$10, _xlfn.XLOOKUP(G18, Q$5:U$5, Q$6:U$10)),"")</f>
         <v/>
       </c>
-      <c r="I18" s="67"/>
-      <c r="J18" s="67"/>
+      <c r="I18" s="57"/>
+      <c r="J18" s="57"/>
       <c r="K18" s="17"/>
       <c r="L18" s="17"/>
       <c r="M18" s="25" t="str" cm="1">
         <f t="array" ref="M18">IFERROR(_xlfn.XLOOKUP(K18, P$6:P$10, _xlfn.XLOOKUP(L18, Q$5:U$5, Q$6:U$10)),"")</f>
         <v/>
       </c>
-      <c r="O18" s="45" t="s">
+      <c r="O18" s="67" t="s">
         <v>33</v>
       </c>
-      <c r="P18" s="45"/>
-      <c r="Q18" s="45"/>
-      <c r="R18" s="45"/>
-    </row>
-    <row r="19" spans="2:21" ht="50.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="71"/>
-      <c r="C19" s="72"/>
-      <c r="D19" s="75" t="s">
+      <c r="P18" s="67"/>
+      <c r="Q18" s="67"/>
+      <c r="R18" s="67"/>
+    </row>
+    <row r="19" spans="2:21" ht="50.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B19" s="61"/>
+      <c r="C19" s="62"/>
+      <c r="D19" s="65" t="s">
         <v>34</v>
       </c>
-      <c r="E19" s="72"/>
+      <c r="E19" s="62"/>
       <c r="F19" s="17"/>
       <c r="G19" s="17"/>
       <c r="H19" s="19" t="str" cm="1">
         <f t="array" ref="H19">IFERROR(_xlfn.XLOOKUP(F19, P$6:P$10, _xlfn.XLOOKUP(G19, Q$5:U$5, Q$6:U$10)),"")</f>
         <v/>
       </c>
-      <c r="I19" s="67"/>
-      <c r="J19" s="67"/>
+      <c r="I19" s="57"/>
+      <c r="J19" s="57"/>
       <c r="K19" s="17"/>
       <c r="L19" s="17"/>
       <c r="M19" s="25" t="str" cm="1">
         <f t="array" ref="M19">IFERROR(_xlfn.XLOOKUP(K19, P$6:P$10, _xlfn.XLOOKUP(L19, Q$5:U$5, Q$6:U$10)),"")</f>
         <v/>
       </c>
-      <c r="O19" s="43" t="s">
+      <c r="O19" s="68" t="s">
         <v>31</v>
       </c>
-      <c r="P19" s="44"/>
+      <c r="P19" s="69"/>
       <c r="Q19" s="5" t="str">
         <f>X$7</f>
         <v>Very Low</v>
@@ -2689,258 +2332,258 @@
         <v>Very High</v>
       </c>
     </row>
-    <row r="20" spans="2:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="71"/>
-      <c r="C20" s="72"/>
-      <c r="D20" s="75" t="s">
+    <row r="20" spans="2:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="61"/>
+      <c r="C20" s="62"/>
+      <c r="D20" s="65" t="s">
         <v>34</v>
       </c>
-      <c r="E20" s="72"/>
+      <c r="E20" s="62"/>
       <c r="F20" s="17"/>
       <c r="G20" s="17"/>
       <c r="H20" s="19" t="str" cm="1">
         <f t="array" ref="H20">IFERROR(_xlfn.XLOOKUP(F20, P$6:P$10, _xlfn.XLOOKUP(G20, Q$5:U$5, Q$6:U$10)),"")</f>
         <v/>
       </c>
-      <c r="I20" s="67"/>
-      <c r="J20" s="67"/>
+      <c r="I20" s="57"/>
+      <c r="J20" s="57"/>
       <c r="K20" s="17"/>
       <c r="L20" s="17"/>
       <c r="M20" s="25" t="str" cm="1">
         <f t="array" ref="M20">IFERROR(_xlfn.XLOOKUP(K20, P$6:P$10, _xlfn.XLOOKUP(L20, Q$5:U$5, Q$6:U$10)),"")</f>
         <v/>
       </c>
-      <c r="O20" s="40" t="s">
+      <c r="O20" s="70" t="s">
         <v>30</v>
       </c>
       <c r="P20" s="27" t="str">
         <f>W$3</f>
         <v>Very High</v>
       </c>
-      <c r="Q20" s="52" t="str">
+      <c r="Q20" s="42" t="str">
         <f>IF(COUNTIFS($K$6:$K$31, $W3, $L$6:$L$31, $X$7)=0, "",COUNTIFS($K$6:$K$31, $W3, $L$6:$L$31, $X$7))</f>
         <v/>
       </c>
-      <c r="R20" s="53" t="str">
+      <c r="R20" s="43" t="str">
         <f>IF(COUNTIFS($K$6:$K$31, $W3, $L$6:$L$31, $X$6)=0, "",COUNTIFS($K$6:$K$31, $W3, $L$6:$L$31, $X$6))</f>
         <v/>
       </c>
-      <c r="S20" s="53" t="str">
+      <c r="S20" s="43" t="str">
         <f>IF(COUNTIFS($K$6:$K$31, $W3, $L$6:$L$31, $X$5)=0, "",COUNTIFS($K$6:$K$31, $W3, $L$6:$L$31, $X$5))</f>
         <v/>
       </c>
-      <c r="T20" s="54" t="str">
+      <c r="T20" s="44" t="str">
         <f>IF(COUNTIFS($K$6:$K$31, $W3, $L$6:$L$31, $X$4)=0, "",COUNTIFS($K$6:$K$31, $W3, $L$6:$L$31, $X$4))</f>
         <v/>
       </c>
-      <c r="U20" s="55" t="str">
+      <c r="U20" s="45" t="str">
         <f>IF(COUNTIFS($K$6:$K$31, $W3, $L$6:$L$31, $X$3)=0, "",COUNTIFS($K$6:$K$31, $W3, $L$6:$L$31, $X$3))</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="2:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="71"/>
-      <c r="C21" s="72"/>
-      <c r="D21" s="75" t="s">
+    <row r="21" spans="2:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B21" s="61"/>
+      <c r="C21" s="62"/>
+      <c r="D21" s="65" t="s">
         <v>34</v>
       </c>
-      <c r="E21" s="72"/>
+      <c r="E21" s="62"/>
       <c r="F21" s="17"/>
       <c r="G21" s="17"/>
       <c r="H21" s="19" t="str" cm="1">
         <f t="array" ref="H21">IFERROR(_xlfn.XLOOKUP(F21, P$6:P$10, _xlfn.XLOOKUP(G21, Q$5:U$5, Q$6:U$10)),"")</f>
         <v/>
       </c>
-      <c r="I21" s="67"/>
-      <c r="J21" s="67"/>
+      <c r="I21" s="57"/>
+      <c r="J21" s="57"/>
       <c r="K21" s="17"/>
       <c r="L21" s="17"/>
       <c r="M21" s="25" t="str" cm="1">
         <f t="array" ref="M21">IFERROR(_xlfn.XLOOKUP(K21, P$6:P$10, _xlfn.XLOOKUP(L21, Q$5:U$5, Q$6:U$10)),"")</f>
         <v/>
       </c>
-      <c r="O21" s="41"/>
+      <c r="O21" s="71"/>
       <c r="P21" s="28" t="str">
         <f>W$4</f>
         <v>High</v>
       </c>
-      <c r="Q21" s="56" t="str">
+      <c r="Q21" s="46" t="str">
         <f t="shared" ref="Q21:Q24" si="5">IF(COUNTIFS($K$6:$K$31, $W4, $L$6:$L$31, $X$7)=0, "",COUNTIFS($K$6:$K$31, $W4, $L$6:$L$31, $X$7))</f>
         <v/>
       </c>
-      <c r="R21" s="57">
+      <c r="R21" s="47">
         <f t="shared" ref="R21:R24" si="6">IF(COUNTIFS($K$6:$K$31, $W4, $L$6:$L$31, $X$6)=0, "",COUNTIFS($K$6:$K$31, $W4, $L$6:$L$31, $X$6))</f>
         <v>1</v>
       </c>
-      <c r="S21" s="58" t="str">
+      <c r="S21" s="48" t="str">
         <f t="shared" ref="S21:S24" si="7">IF(COUNTIFS($K$6:$K$31, $W4, $L$6:$L$31, $X$5)=0, "",COUNTIFS($K$6:$K$31, $W4, $L$6:$L$31, $X$5))</f>
         <v/>
       </c>
-      <c r="T21" s="59" t="str">
+      <c r="T21" s="49" t="str">
         <f t="shared" ref="T21:T24" si="8">IF(COUNTIFS($K$6:$K$31, $W4, $L$6:$L$31, $X$4)=0, "",COUNTIFS($K$6:$K$31, $W4, $L$6:$L$31, $X$4))</f>
         <v/>
       </c>
-      <c r="U21" s="60" t="str">
+      <c r="U21" s="50" t="str">
         <f t="shared" ref="U21:U24" si="9">IF(COUNTIFS($K$6:$K$31, $W4, $L$6:$L$31, $X$3)=0, "",COUNTIFS($K$6:$K$31, $W4, $L$6:$L$31, $X$3))</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="2:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="71"/>
-      <c r="C22" s="72"/>
-      <c r="D22" s="75" t="s">
+    <row r="22" spans="2:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B22" s="61"/>
+      <c r="C22" s="62"/>
+      <c r="D22" s="65" t="s">
         <v>34</v>
       </c>
-      <c r="E22" s="72"/>
+      <c r="E22" s="62"/>
       <c r="F22" s="17"/>
       <c r="G22" s="17"/>
       <c r="H22" s="19" t="str" cm="1">
         <f t="array" ref="H22">IFERROR(_xlfn.XLOOKUP(F22, P$6:P$10, _xlfn.XLOOKUP(G22, Q$5:U$5, Q$6:U$10)),"")</f>
         <v/>
       </c>
-      <c r="I22" s="67"/>
-      <c r="J22" s="67"/>
+      <c r="I22" s="57"/>
+      <c r="J22" s="57"/>
       <c r="K22" s="17"/>
       <c r="L22" s="17"/>
       <c r="M22" s="25" t="str" cm="1">
         <f t="array" ref="M22">IFERROR(_xlfn.XLOOKUP(K22, P$6:P$10, _xlfn.XLOOKUP(L22, Q$5:U$5, Q$6:U$10)),"")</f>
         <v/>
       </c>
-      <c r="O22" s="41"/>
+      <c r="O22" s="71"/>
       <c r="P22" s="28" t="str">
         <f>W$5</f>
         <v>Medium</v>
       </c>
-      <c r="Q22" s="56">
+      <c r="Q22" s="46">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="R22" s="57" t="str">
+      <c r="R22" s="47" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="S22" s="57" t="str">
+      <c r="S22" s="47" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="T22" s="58" t="str">
+      <c r="T22" s="48" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="U22" s="60" t="str">
+      <c r="U22" s="50" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="23" spans="2:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="71"/>
-      <c r="C23" s="72"/>
-      <c r="D23" s="75" t="s">
+    <row r="23" spans="2:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B23" s="61"/>
+      <c r="C23" s="62"/>
+      <c r="D23" s="65" t="s">
         <v>34</v>
       </c>
-      <c r="E23" s="72"/>
+      <c r="E23" s="62"/>
       <c r="F23" s="17"/>
       <c r="G23" s="17"/>
       <c r="H23" s="19" t="str" cm="1">
         <f t="array" ref="H23">IFERROR(_xlfn.XLOOKUP(F23, P$6:P$10, _xlfn.XLOOKUP(G23, Q$5:U$5, Q$6:U$10)),"")</f>
         <v/>
       </c>
-      <c r="I23" s="67"/>
-      <c r="J23" s="67"/>
+      <c r="I23" s="57"/>
+      <c r="J23" s="57"/>
       <c r="K23" s="17"/>
       <c r="L23" s="17"/>
       <c r="M23" s="25" t="str" cm="1">
         <f t="array" ref="M23">IFERROR(_xlfn.XLOOKUP(K23, P$6:P$10, _xlfn.XLOOKUP(L23, Q$5:U$5, Q$6:U$10)),"")</f>
         <v/>
       </c>
-      <c r="O23" s="41"/>
+      <c r="O23" s="71"/>
       <c r="P23" s="28" t="str">
         <f>W$6</f>
         <v>Low</v>
       </c>
-      <c r="Q23" s="56" t="str">
+      <c r="Q23" s="46" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="R23" s="61" t="str">
+      <c r="R23" s="51" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="S23" s="57" t="str">
+      <c r="S23" s="47" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="T23" s="58" t="str">
+      <c r="T23" s="48" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="U23" s="60" t="str">
+      <c r="U23" s="50" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="24" spans="2:21" ht="50.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="71"/>
-      <c r="C24" s="72"/>
-      <c r="D24" s="75" t="s">
+    <row r="24" spans="2:21" ht="50.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B24" s="61"/>
+      <c r="C24" s="62"/>
+      <c r="D24" s="65" t="s">
         <v>34</v>
       </c>
-      <c r="E24" s="72"/>
+      <c r="E24" s="62"/>
       <c r="F24" s="17"/>
       <c r="G24" s="17"/>
       <c r="H24" s="19" t="str" cm="1">
         <f t="array" ref="H24">IFERROR(_xlfn.XLOOKUP(F24, P$6:P$10, _xlfn.XLOOKUP(G24, Q$5:U$5, Q$6:U$10)),"")</f>
         <v/>
       </c>
-      <c r="I24" s="67"/>
-      <c r="J24" s="67"/>
+      <c r="I24" s="57"/>
+      <c r="J24" s="57"/>
       <c r="K24" s="17"/>
       <c r="L24" s="17"/>
       <c r="M24" s="25" t="str" cm="1">
         <f t="array" ref="M24">IFERROR(_xlfn.XLOOKUP(K24, P$6:P$10, _xlfn.XLOOKUP(L24, Q$5:U$5, Q$6:U$10)),"")</f>
         <v/>
       </c>
-      <c r="O24" s="42"/>
+      <c r="O24" s="72"/>
       <c r="P24" s="29" t="str">
         <f>W$7</f>
         <v>Very Low</v>
       </c>
-      <c r="Q24" s="62" t="str">
+      <c r="Q24" s="52" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="R24" s="63" t="str">
+      <c r="R24" s="53" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="S24" s="63" t="str">
+      <c r="S24" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="T24" s="64" t="str">
+      <c r="T24" s="54" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="U24" s="65" t="str">
+      <c r="U24" s="55" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="25" spans="2:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="71"/>
-      <c r="C25" s="72"/>
-      <c r="D25" s="75" t="s">
+    <row r="25" spans="2:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B25" s="61"/>
+      <c r="C25" s="62"/>
+      <c r="D25" s="65" t="s">
         <v>34</v>
       </c>
-      <c r="E25" s="72"/>
+      <c r="E25" s="62"/>
       <c r="F25" s="17"/>
       <c r="G25" s="17"/>
       <c r="H25" s="19" t="str" cm="1">
         <f t="array" ref="H25">IFERROR(_xlfn.XLOOKUP(F25, P$6:P$10, _xlfn.XLOOKUP(G25, Q$5:U$5, Q$6:U$10)),"")</f>
         <v/>
       </c>
-      <c r="I25" s="67"/>
-      <c r="J25" s="67"/>
+      <c r="I25" s="57"/>
+      <c r="J25" s="57"/>
       <c r="K25" s="17"/>
       <c r="L25" s="17"/>
       <c r="M25" s="25" t="str" cm="1">
@@ -2948,21 +2591,21 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="2:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="71"/>
-      <c r="C26" s="72"/>
-      <c r="D26" s="75" t="s">
+    <row r="26" spans="2:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B26" s="61"/>
+      <c r="C26" s="62"/>
+      <c r="D26" s="65" t="s">
         <v>34</v>
       </c>
-      <c r="E26" s="72"/>
+      <c r="E26" s="62"/>
       <c r="F26" s="17"/>
       <c r="G26" s="17"/>
       <c r="H26" s="19" t="str" cm="1">
         <f t="array" ref="H26">IFERROR(_xlfn.XLOOKUP(F26, P$6:P$10, _xlfn.XLOOKUP(G26, Q$5:U$5, Q$6:U$10)),"")</f>
         <v/>
       </c>
-      <c r="I26" s="67"/>
-      <c r="J26" s="67"/>
+      <c r="I26" s="57"/>
+      <c r="J26" s="57"/>
       <c r="K26" s="17"/>
       <c r="L26" s="17"/>
       <c r="M26" s="25" t="str" cm="1">
@@ -2970,21 +2613,21 @@
         <v/>
       </c>
     </row>
-    <row r="27" spans="2:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="71"/>
-      <c r="C27" s="72"/>
-      <c r="D27" s="75" t="s">
+    <row r="27" spans="2:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B27" s="61"/>
+      <c r="C27" s="62"/>
+      <c r="D27" s="65" t="s">
         <v>34</v>
       </c>
-      <c r="E27" s="72"/>
+      <c r="E27" s="62"/>
       <c r="F27" s="17"/>
       <c r="G27" s="17"/>
       <c r="H27" s="19" t="str" cm="1">
         <f t="array" ref="H27">IFERROR(_xlfn.XLOOKUP(F27, P$6:P$10, _xlfn.XLOOKUP(G27, Q$5:U$5, Q$6:U$10)),"")</f>
         <v/>
       </c>
-      <c r="I27" s="67"/>
-      <c r="J27" s="67"/>
+      <c r="I27" s="57"/>
+      <c r="J27" s="57"/>
       <c r="K27" s="17"/>
       <c r="L27" s="17"/>
       <c r="M27" s="25" t="str" cm="1">
@@ -2992,21 +2635,21 @@
         <v/>
       </c>
     </row>
-    <row r="28" spans="2:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="71"/>
-      <c r="C28" s="72"/>
-      <c r="D28" s="75" t="s">
+    <row r="28" spans="2:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B28" s="61"/>
+      <c r="C28" s="62"/>
+      <c r="D28" s="65" t="s">
         <v>34</v>
       </c>
-      <c r="E28" s="72"/>
+      <c r="E28" s="62"/>
       <c r="F28" s="17"/>
       <c r="G28" s="17"/>
       <c r="H28" s="19" t="str" cm="1">
         <f t="array" ref="H28">IFERROR(_xlfn.XLOOKUP(F28, P$6:P$10, _xlfn.XLOOKUP(G28, Q$5:U$5, Q$6:U$10)),"")</f>
         <v/>
       </c>
-      <c r="I28" s="67"/>
-      <c r="J28" s="67"/>
+      <c r="I28" s="57"/>
+      <c r="J28" s="57"/>
       <c r="K28" s="17"/>
       <c r="L28" s="17"/>
       <c r="M28" s="25" t="str" cm="1">
@@ -3014,21 +2657,21 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="2:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="71"/>
-      <c r="C29" s="72"/>
-      <c r="D29" s="75" t="s">
+    <row r="29" spans="2:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B29" s="61"/>
+      <c r="C29" s="62"/>
+      <c r="D29" s="65" t="s">
         <v>34</v>
       </c>
-      <c r="E29" s="72"/>
+      <c r="E29" s="62"/>
       <c r="F29" s="17"/>
       <c r="G29" s="17"/>
       <c r="H29" s="19" t="str" cm="1">
         <f t="array" ref="H29">IFERROR(_xlfn.XLOOKUP(F29, P$6:P$10, _xlfn.XLOOKUP(G29, Q$5:U$5, Q$6:U$10)),"")</f>
         <v/>
       </c>
-      <c r="I29" s="67"/>
-      <c r="J29" s="67"/>
+      <c r="I29" s="57"/>
+      <c r="J29" s="57"/>
       <c r="K29" s="17"/>
       <c r="L29" s="17"/>
       <c r="M29" s="25" t="str" cm="1">
@@ -3036,21 +2679,21 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="2:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="71"/>
-      <c r="C30" s="72"/>
-      <c r="D30" s="75" t="s">
+    <row r="30" spans="2:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B30" s="61"/>
+      <c r="C30" s="62"/>
+      <c r="D30" s="65" t="s">
         <v>34</v>
       </c>
-      <c r="E30" s="72"/>
+      <c r="E30" s="62"/>
       <c r="F30" s="17"/>
       <c r="G30" s="17"/>
       <c r="H30" s="19" t="str" cm="1">
         <f t="array" ref="H30">IFERROR(_xlfn.XLOOKUP(F30, P$6:P$10, _xlfn.XLOOKUP(G30, Q$5:U$5, Q$6:U$10)),"")</f>
         <v/>
       </c>
-      <c r="I30" s="67"/>
-      <c r="J30" s="67"/>
+      <c r="I30" s="57"/>
+      <c r="J30" s="57"/>
       <c r="K30" s="17"/>
       <c r="L30" s="17"/>
       <c r="M30" s="25" t="str" cm="1">
@@ -3058,21 +2701,21 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="2:21" ht="50.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B31" s="73"/>
-      <c r="C31" s="74"/>
-      <c r="D31" s="76" t="s">
+    <row r="31" spans="2:21" ht="50.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B31" s="63"/>
+      <c r="C31" s="64"/>
+      <c r="D31" s="66" t="s">
         <v>34</v>
       </c>
-      <c r="E31" s="74"/>
+      <c r="E31" s="64"/>
       <c r="F31" s="18"/>
       <c r="G31" s="18"/>
       <c r="H31" s="18" t="str" cm="1">
         <f t="array" ref="H31">IFERROR(_xlfn.XLOOKUP(F31, P$6:P$10, _xlfn.XLOOKUP(G31, Q$5:U$5, Q$6:U$10)),"")</f>
         <v/>
       </c>
-      <c r="I31" s="68"/>
-      <c r="J31" s="68"/>
+      <c r="I31" s="58"/>
+      <c r="J31" s="58"/>
       <c r="K31" s="18"/>
       <c r="L31" s="18"/>
       <c r="M31" s="26" t="str" cm="1">
@@ -3082,44 +2725,44 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="O18:R18"/>
-    <mergeCell ref="O19:P19"/>
-    <mergeCell ref="O20:O24"/>
-    <mergeCell ref="O12:P12"/>
-    <mergeCell ref="O13:O17"/>
+    <mergeCell ref="O11:R11"/>
     <mergeCell ref="O6:O10"/>
     <mergeCell ref="B1:M1"/>
     <mergeCell ref="F2:H2"/>
     <mergeCell ref="F4:H4"/>
     <mergeCell ref="K4:M4"/>
     <mergeCell ref="O5:P5"/>
-    <mergeCell ref="O11:R11"/>
+    <mergeCell ref="O18:R18"/>
+    <mergeCell ref="O19:P19"/>
+    <mergeCell ref="O20:O24"/>
+    <mergeCell ref="O12:P12"/>
+    <mergeCell ref="O13:O17"/>
   </mergeCells>
   <conditionalFormatting sqref="H6:H31">
-    <cfRule type="containsText" dxfId="15" priority="6" operator="containsText" text="Critical">
+    <cfRule type="containsText" dxfId="7" priority="6" operator="containsText" text="Critical">
       <formula>NOT(ISERROR(SEARCH("Critical",H6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="14" priority="7" operator="containsText" text="Sustainable">
+    <cfRule type="containsText" dxfId="6" priority="7" operator="containsText" text="Sustainable">
       <formula>NOT(ISERROR(SEARCH("Sustainable",H6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="13" priority="8" operator="containsText" text="Moderate">
+    <cfRule type="containsText" dxfId="5" priority="8" operator="containsText" text="Moderate">
       <formula>NOT(ISERROR(SEARCH("Moderate",H6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="12" priority="9" operator="containsText" text="Severe">
+    <cfRule type="containsText" dxfId="4" priority="9" operator="containsText" text="Severe">
       <formula>NOT(ISERROR(SEARCH("Severe",H6)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M6:M31">
-    <cfRule type="containsText" dxfId="11" priority="2" operator="containsText" text="Severe">
+    <cfRule type="containsText" dxfId="3" priority="2" operator="containsText" text="Severe">
       <formula>NOT(ISERROR(SEARCH("Severe",M6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="10" priority="3" operator="containsText" text="Moderate">
+    <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="Moderate">
       <formula>NOT(ISERROR(SEARCH("Moderate",M6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="8" priority="4" operator="containsText" text="Critical">
+    <cfRule type="containsText" dxfId="1" priority="4" operator="containsText" text="Critical">
       <formula>NOT(ISERROR(SEARCH("Critical",M6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="9" priority="5" operator="containsText" text="Sustainable">
+    <cfRule type="containsText" dxfId="0" priority="5" operator="containsText" text="Sustainable">
       <formula>NOT(ISERROR(SEARCH("Sustainable",M6)))</formula>
     </cfRule>
   </conditionalFormatting>
